--- a/02-Execucao/01-Questionario/04-Resultados_iGovTI/03-pos-comentarios-gestor/comparacao-2023-2026/20260716-comparacao-iGovTI-2023-2026.xlsx
+++ b/02-Execucao/01-Questionario/04-Resultados_iGovTI/03-pos-comentarios-gestor/comparacao-2023-2026/20260716-comparacao-iGovTI-2023-2026.xlsx
@@ -1313,10 +1313,10 @@
         <v>0.553945959583809</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4034908296573994</v>
+        <v>0.417536073251657</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1504551299264096</v>
+        <v>-0.136409886332152</v>
       </c>
       <c r="J5" t="n">
         <v>0.4339385533163037</v>
@@ -1331,10 +1331,10 @@
         <v>0.6739533658513143</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3379562854650782</v>
+        <v>0.3660467726535935</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.335997080386236</v>
+        <v>-0.3079065931977208</v>
       </c>
       <c r="P5" t="n">
         <v>0.5</v>
@@ -1367,10 +1367,10 @@
         <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.6174999999999999</v>
+        <v>0.7025</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.3825000000000001</v>
+        <v>-0.2975</v>
       </c>
       <c r="AB5" t="n">
         <v>0.7466798465063026</v>
@@ -2268,10 +2268,10 @@
         <v>0.4092267544642821</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6619023815575781</v>
+        <v>0.6636765201862554</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2526756270932959</v>
+        <v>0.2544497657219733</v>
       </c>
       <c r="J10" t="n">
         <v>0.5410969924372614</v>
@@ -2286,10 +2286,10 @@
         <v>0.2773565164913028</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4871434185024624</v>
+        <v>0.4906916957598171</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2097869020111596</v>
+        <v>0.2133351792685143</v>
       </c>
       <c r="P10" t="n">
         <v>0.7166666666666667</v>
@@ -2340,10 +2340,10 @@
         <v>0.1203922953183441</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.5282490061751518</v>
+        <v>0.5733156286047514</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.4078567108568077</v>
+        <v>0.4529233332864073</v>
       </c>
       <c r="AH10" t="n">
         <v>0.2916666666666666</v>
@@ -2376,10 +2376,10 @@
         <v>0.461087366589325</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.5994298960423504</v>
+        <v>0.6249681045705874</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.1383425294530254</v>
+        <v>0.1638807379812623</v>
       </c>
       <c r="AT10" t="n">
         <v>0.05</v>
@@ -7799,19 +7799,19 @@
         <v>0.6777257448181767</v>
       </c>
       <c r="H39" t="n">
-        <v>0.5368334965420798</v>
+        <v>0.5530063887842832</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1408922482760969</v>
+        <v>-0.1247193560338935</v>
       </c>
       <c r="J39" t="n">
         <v>0.7014689449943675</v>
       </c>
       <c r="K39" t="n">
-        <v>0.5794529442739249</v>
+        <v>0.6117987287583319</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.1220160007204426</v>
+        <v>-0.08967021623603566</v>
       </c>
       <c r="M39" t="n">
         <v>0.6539825446419859</v>
@@ -7826,10 +7826,10 @@
         <v>0.9055555555555556</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.6222222222222222</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="R39" t="n">
-        <v>-0.2833333333333333</v>
+        <v>-0.1888888888888889</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -13844,13 +13844,13 @@
         <v>0.1419437973010805</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1888639371949954</v>
+        <v>0.1893344118194827</v>
       </c>
       <c r="F2" t="n">
         <v>0.1310647725067063</v>
       </c>
       <c r="G2" t="n">
-        <v>0.008747997065792894</v>
+        <v>0.009218471690280221</v>
       </c>
       <c r="H2" t="n">
         <v>-0.003615056546364903</v>
@@ -13883,13 +13883,13 @@
         <v>0.1107410365535664</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1617766021978861</v>
+        <v>0.1622522754991274</v>
       </c>
       <c r="F3" t="n">
         <v>0.09799077653095961</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01056970847718976</v>
+        <v>0.01104538177843104</v>
       </c>
       <c r="H3" t="n">
         <v>-0.004320705738215636</v>
@@ -13922,13 +13922,13 @@
         <v>0.1633936074882846</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2159512721921046</v>
+        <v>0.216416548139838</v>
       </c>
       <c r="F4" t="n">
         <v>0.1533631689949307</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006926285654396026</v>
+        <v>0.007391561602129413</v>
       </c>
       <c r="H4" t="n">
         <v>-0.006359279569859079</v>
@@ -13961,13 +13961,13 @@
         <v>0.15</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2075163398692811</v>
+        <v>0.20890522875817</v>
       </c>
       <c r="F5" t="n">
         <v>0.1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02990196078431372</v>
+        <v>0.03129084967320261</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -14078,13 +14078,13 @@
         <v>0.15</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3922242647058823</v>
+        <v>0.3934742647058823</v>
       </c>
       <c r="F8" t="n">
         <v>0.3</v>
       </c>
       <c r="G8" t="n">
-        <v>0.09885066526610645</v>
+        <v>0.1001006652661065</v>
       </c>
       <c r="H8" t="n">
         <v>0.04791666666666666</v>
@@ -14156,13 +14156,13 @@
         <v>0.1056736956852704</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1844461112449648</v>
+        <v>0.185108855692459</v>
       </c>
       <c r="F10" t="n">
         <v>0.1010912703084124</v>
       </c>
       <c r="G10" t="n">
-        <v>0.03486384577525296</v>
+        <v>0.03552659022274707</v>
       </c>
       <c r="H10" t="n">
         <v>0.001033627972744717</v>
@@ -14312,13 +14312,13 @@
         <v>0.1212478595974801</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2189101153808957</v>
+        <v>0.2192856772710168</v>
       </c>
       <c r="F14" t="n">
         <v>0.1741985329641795</v>
       </c>
       <c r="G14" t="n">
-        <v>0.04711976955329984</v>
+        <v>0.04749533144342098</v>
       </c>
       <c r="H14" t="n">
         <v>0.04185911289776773</v>
@@ -15483,10 +15483,10 @@
         <v>0.553945959583809</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4034908296573994</v>
+        <v>0.417536073251657</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1504551299264096</v>
+        <v>-0.136409886332152</v>
       </c>
       <c r="M5" t="n">
         <v>0.4339385533163037</v>
@@ -15501,10 +15501,10 @@
         <v>0.6739533658513143</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3379562854650782</v>
+        <v>0.3660467726535935</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.335997080386236</v>
+        <v>-0.3079065931977208</v>
       </c>
       <c r="S5" t="n">
         <v>0.5</v>
@@ -15537,10 +15537,10 @@
         <v>1</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.6174999999999999</v>
+        <v>0.7025</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.3825000000000001</v>
+        <v>-0.2975</v>
       </c>
       <c r="AE5" t="n">
         <v>0.7466798465063026</v>
@@ -16428,10 +16428,10 @@
         <v>0.4092267544642821</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6619023815575781</v>
+        <v>0.6636765201862554</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2526756270932959</v>
+        <v>0.2544497657219733</v>
       </c>
       <c r="M10" t="n">
         <v>0.5410969924372614</v>
@@ -16446,10 +16446,10 @@
         <v>0.2773565164913028</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4871434185024624</v>
+        <v>0.4906916957598171</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2097869020111596</v>
+        <v>0.2133351792685143</v>
       </c>
       <c r="S10" t="n">
         <v>0.7166666666666667</v>
@@ -16500,10 +16500,10 @@
         <v>0.1203922953183441</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.5282490061751518</v>
+        <v>0.5733156286047514</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.4078567108568077</v>
+        <v>0.4529233332864073</v>
       </c>
       <c r="AK10" t="n">
         <v>0.2916666666666666</v>
@@ -16536,10 +16536,10 @@
         <v>0.461087366589325</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.5994298960423504</v>
+        <v>0.6249681045705874</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.1383425294530254</v>
+        <v>0.1638807379812623</v>
       </c>
       <c r="AW10" t="n">
         <v>0.05</v>
@@ -22371,19 +22371,19 @@
         <v>0.6777257448181767</v>
       </c>
       <c r="K45" t="n">
-        <v>0.5368334965420798</v>
+        <v>0.5530063887842832</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.1408922482760969</v>
+        <v>-0.1247193560338935</v>
       </c>
       <c r="M45" t="n">
         <v>0.7014689449943675</v>
       </c>
       <c r="N45" t="n">
-        <v>0.5794529442739249</v>
+        <v>0.6117987287583319</v>
       </c>
       <c r="O45" t="n">
-        <v>-0.1220160007204426</v>
+        <v>-0.08967021623603566</v>
       </c>
       <c r="P45" t="n">
         <v>0.6539825446419859</v>
@@ -22398,10 +22398,10 @@
         <v>0.9055555555555556</v>
       </c>
       <c r="T45" t="n">
-        <v>0.6222222222222222</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="U45" t="n">
-        <v>-0.2833333333333333</v>
+        <v>-0.1888888888888889</v>
       </c>
       <c r="V45" t="n">
         <v>1</v>

--- a/02-Execucao/01-Questionario/04-Resultados_iGovTI/03-pos-comentarios-gestor/comparacao-2023-2026/20260716-comparacao-iGovTI-2023-2026.xlsx
+++ b/02-Execucao/01-Questionario/04-Resultados_iGovTI/03-pos-comentarios-gestor/comparacao-2023-2026/20260716-comparacao-iGovTI-2023-2026.xlsx
@@ -1313,10 +1313,10 @@
         <v>0.553945959583809</v>
       </c>
       <c r="H5" t="n">
-        <v>0.417536073251657</v>
+        <v>0.4034908296573994</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.136409886332152</v>
+        <v>-0.1504551299264096</v>
       </c>
       <c r="J5" t="n">
         <v>0.4339385533163037</v>
@@ -1331,10 +1331,10 @@
         <v>0.6739533658513143</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3660467726535935</v>
+        <v>0.3379562854650782</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3079065931977208</v>
+        <v>-0.335997080386236</v>
       </c>
       <c r="P5" t="n">
         <v>0.5</v>
@@ -1367,10 +1367,10 @@
         <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.7025</v>
+        <v>0.6174999999999999</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.2975</v>
+        <v>-0.3825000000000001</v>
       </c>
       <c r="AB5" t="n">
         <v>0.7466798465063026</v>
@@ -2268,10 +2268,10 @@
         <v>0.4092267544642821</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6636765201862554</v>
+        <v>0.6759476251518357</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2544497657219733</v>
+        <v>0.2667208706875536</v>
       </c>
       <c r="J10" t="n">
         <v>0.5410969924372614</v>
@@ -2286,10 +2286,10 @@
         <v>0.2773565164913028</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4906916957598171</v>
+        <v>0.5152339056909777</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2133351792685143</v>
+        <v>0.2378773891996749</v>
       </c>
       <c r="P10" t="n">
         <v>0.7166666666666667</v>
@@ -2322,10 +2322,10 @@
         <v>0.4130952380952381</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.915</v>
+        <v>1</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.5019047619047619</v>
+        <v>0.5869047619047618</v>
       </c>
       <c r="AB10" t="n">
         <v>0.2474883688541739</v>
@@ -2340,10 +2340,10 @@
         <v>0.1203922953183441</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.5733156286047514</v>
+        <v>0.5282490061751518</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.4529233332864073</v>
+        <v>0.4078567108568077</v>
       </c>
       <c r="AH10" t="n">
         <v>0.2916666666666666</v>
@@ -2376,10 +2376,10 @@
         <v>0.461087366589325</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.6249681045705874</v>
+        <v>0.5994298960423504</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.1638807379812623</v>
+        <v>0.1383425294530254</v>
       </c>
       <c r="AT10" t="n">
         <v>0.05</v>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>Gestão de projetos de TIC (+0.6800); Monitoramento e avaliação de TIC (+0.5416); Planejamento de TIC (+0.5019)</t>
+          <t>Gestão de projetos de TIC (+0.6800); Planejamento de TIC (+0.5869); Monitoramento e avaliação de TIC (+0.5416)</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -3163,10 +3163,10 @@
         <v>0.6246033058004061</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.167173482808753</v>
+        <v>0.138753990731265</v>
       </c>
       <c r="BB14" t="n">
-        <v>-0.4574298229916531</v>
+        <v>-0.4858493150691411</v>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>Processos de contratação de TIC (-0.4574); Processo de software (-0.3792); Gestão de pessoas de TIC (-0.3412)</t>
+          <t>Processos de contratação de TIC (-0.4858); Processo de software (-0.3792); Gestão de pessoas de TIC (-0.3412)</t>
         </is>
       </c>
     </row>
@@ -3792,10 +3792,10 @@
         <v>0.2459554087171204</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3018951793437764</v>
+        <v>0.3054830036092623</v>
       </c>
       <c r="I18" t="n">
-        <v>0.05593977062665603</v>
+        <v>0.05952759489214191</v>
       </c>
       <c r="J18" t="n">
         <v>0.0327821959341698</v>
@@ -3810,10 +3810,10 @@
         <v>0.4591286215000709</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4132183981714049</v>
+        <v>0.4203940467023767</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.04591022332866607</v>
+        <v>-0.03873457479769427</v>
       </c>
       <c r="P18" t="n">
         <v>0.05</v>
@@ -3864,10 +3864,10 @@
         <v>0.1500000000000001</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.1146545354858269</v>
+        <v>0.2167636551934384</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0.03534546451417324</v>
+        <v>0.06676365519343827</v>
       </c>
       <c r="AH18" t="n">
         <v>0.15</v>
@@ -3900,10 +3900,10 @@
         <v>0.15</v>
       </c>
       <c r="AR18" t="n">
-        <v>0.1745340408288195</v>
+        <v>0.184298316440158</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.02453404082881949</v>
+        <v>0.03429831644015802</v>
       </c>
       <c r="AT18" t="n">
         <v>0.15</v>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>Estrutura de segurança da informação (+0.6208); Resultados de TIC (+0.4643); Monitoramento e avaliação de TIC (+0.0360)</t>
+          <t>Estrutura de segurança da informação (+0.6208); Resultados de TIC (+0.4643); Gestão de serviços de TIC (+0.0668)</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -4174,10 +4174,10 @@
         <v>0.08707115530501731</v>
       </c>
       <c r="H20" t="n">
-        <v>0.05391629137736587</v>
+        <v>0.05396013116243505</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.03315486392765144</v>
+        <v>-0.03311102414258226</v>
       </c>
       <c r="J20" t="n">
         <v>0.1200443376860425</v>
@@ -4192,10 +4192,10 @@
         <v>0.05409797292399215</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1078325827547317</v>
+        <v>0.1079202623248701</v>
       </c>
       <c r="O20" t="n">
-        <v>0.05373460983073956</v>
+        <v>0.05382228940087796</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -4282,10 +4282,10 @@
         <v>0.02202601891170285</v>
       </c>
       <c r="AR20" t="n">
-        <v>0.1597642756113385</v>
+        <v>0.1646464134170078</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.1377382566996356</v>
+        <v>0.1426203945053049</v>
       </c>
       <c r="AT20" t="n">
         <v>0</v>
@@ -4556,10 +4556,10 @@
         <v>0.2116562372713717</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2778395755053683</v>
+        <v>0.2758361132448119</v>
       </c>
       <c r="I22" t="n">
-        <v>0.06618333823399661</v>
+        <v>0.06417987597344019</v>
       </c>
       <c r="J22" t="n">
         <v>0.1107410365535664</v>
@@ -4574,10 +4574,10 @@
         <v>0.312571437989177</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3185729436556963</v>
+        <v>0.3145660191345835</v>
       </c>
       <c r="O22" t="n">
-        <v>0.006001505666519247</v>
+        <v>0.00199458114540646</v>
       </c>
       <c r="P22" t="n">
         <v>0.15</v>
@@ -4628,10 +4628,10 @@
         <v>0.3879760135726121</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.5244755941505904</v>
+        <v>0.4794089717209908</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.1364995805779783</v>
+        <v>0.09143295814837865</v>
       </c>
       <c r="AH22" t="n">
         <v>0.15</v>
@@ -4664,10 +4664,10 @@
         <v>0.1009335249995757</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.5491780097330067</v>
+        <v>0.4981015926765328</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.448244484733431</v>
+        <v>0.3971680676769571</v>
       </c>
       <c r="AT22" t="n">
         <v>0.15</v>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>Resultados de TIC (+0.6071); Estrutura de segurança da informação (+0.5326); Processos de segurança da informação (+0.4482)</t>
+          <t>Resultados de TIC (+0.6071); Estrutura de segurança da informação (+0.5326); Gestão de riscos de TIC (+0.4186)</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -7799,10 +7799,10 @@
         <v>0.6777257448181767</v>
       </c>
       <c r="H39" t="n">
-        <v>0.5530063887842832</v>
+        <v>0.5389611451900256</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1247193560338935</v>
+        <v>-0.1387645996281511</v>
       </c>
       <c r="J39" t="n">
         <v>0.7014689449943675</v>
@@ -7817,10 +7817,10 @@
         <v>0.6539825446419859</v>
       </c>
       <c r="N39" t="n">
-        <v>0.4942140488102346</v>
+        <v>0.4661235616217193</v>
       </c>
       <c r="O39" t="n">
-        <v>-0.1597684958317513</v>
+        <v>-0.1878589830202666</v>
       </c>
       <c r="P39" t="n">
         <v>0.9055555555555556</v>
@@ -7853,10 +7853,10 @@
         <v>0.6053571428571428</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.8300000000000001</v>
+        <v>0.745</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.2246428571428573</v>
+        <v>0.1396428571428572</v>
       </c>
       <c r="AB39" t="n">
         <v>0.7885170495992505</v>
@@ -7946,7 +7946,7 @@
       </c>
       <c r="BD39" t="inlineStr">
         <is>
-          <t>Planejamento de TIC (+0.2246); Processo de software (+0.2125); Gestão de níveis de serviço (+0.1417)</t>
+          <t>Processo de software (+0.2125); Gestão de níveis de serviço (+0.1417); Planejamento de TIC (+0.1396)</t>
         </is>
       </c>
       <c r="BE39" t="inlineStr">
@@ -8754,10 +8754,10 @@
         <v>0.04263031711956485</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1806676605496295</v>
+        <v>0.1947129041438871</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1380373434300646</v>
+        <v>0.1520825870243222</v>
       </c>
       <c r="J44" t="n">
         <v>0.0469738712684514</v>
@@ -8772,10 +8772,10 @@
         <v>0.0382867629706783</v>
       </c>
       <c r="N44" t="n">
-        <v>0.309962604565201</v>
+        <v>0.3380530917537163</v>
       </c>
       <c r="O44" t="n">
-        <v>0.2716758415945227</v>
+        <v>0.299766328783038</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
@@ -8808,10 +8808,10 @@
         <v>0.075</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.42625</v>
+        <v>0.51125</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.35125</v>
+        <v>0.43625</v>
       </c>
       <c r="AB44" t="n">
         <v>0.03540735591510425</v>
@@ -8901,7 +8901,7 @@
       </c>
       <c r="BD44" t="inlineStr">
         <is>
-          <t>Processo de software (+0.5000); Gestão de níveis de serviço (+0.4333); Gestão de serviços de TIC (+0.4055)</t>
+          <t>Processo de software (+0.5000); Planejamento de TIC (+0.4362); Gestão de níveis de serviço (+0.4333)</t>
         </is>
       </c>
       <c r="BE44" t="inlineStr">
@@ -8945,19 +8945,19 @@
         <v>0.1933337468966435</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1293393206258521</v>
+        <v>0.13599874684323</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.06399442627079135</v>
+        <v>-0.05733500005341347</v>
       </c>
       <c r="J45" t="n">
         <v>0.2465983387501051</v>
       </c>
       <c r="K45" t="n">
-        <v>0.1518389316326444</v>
+        <v>0.1651577840674002</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.0947594071174607</v>
+        <v>-0.08144055468270489</v>
       </c>
       <c r="M45" t="n">
         <v>0.1400691550431818</v>
@@ -8972,10 +8972,10 @@
         <v>0.3444444444444444</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.2277777777777778</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="R45" t="n">
-        <v>-0.1166666666666666</v>
+        <v>-0.07777777777777772</v>
       </c>
       <c r="S45" t="n">
         <v>0.07798508700049113</v>
@@ -9320,35 +9320,35 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Iniciando</t>
+          <t>Intermediário</t>
         </is>
       </c>
       <c r="G47" t="n">
         <v>0.1873441488767208</v>
       </c>
       <c r="H47" t="n">
-        <v>0.3961517396969197</v>
+        <v>0.421132769125894</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2088075908201989</v>
+        <v>0.2337886202491732</v>
       </c>
       <c r="J47" t="n">
         <v>0.06376716528511499</v>
       </c>
       <c r="K47" t="n">
-        <v>0.2159932093886675</v>
+        <v>0.2986228677290474</v>
       </c>
       <c r="L47" t="n">
-        <v>0.1522260441035525</v>
+        <v>0.2348557024439324</v>
       </c>
       <c r="M47" t="n">
         <v>0.3109211324683265</v>
       </c>
       <c r="N47" t="n">
-        <v>0.576310270005172</v>
+        <v>0.5436426705227406</v>
       </c>
       <c r="O47" t="n">
-        <v>0.2653891375368455</v>
+        <v>0.2327215380544141</v>
       </c>
       <c r="P47" t="n">
         <v>0.15</v>
@@ -9363,10 +9363,10 @@
         <v>0.03599311707714975</v>
       </c>
       <c r="T47" t="n">
-        <v>0.380399470228791</v>
+        <v>0.620353584076456</v>
       </c>
       <c r="U47" t="n">
-        <v>0.3444063531516413</v>
+        <v>0.5843604669993063</v>
       </c>
       <c r="V47" t="n">
         <v>0</v>
@@ -9381,10 +9381,10 @@
         <v>0.5142857142857142</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.915</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.4007142857142858</v>
+        <v>0.3157142857142858</v>
       </c>
       <c r="AB47" t="n">
         <v>0.3276261949251849</v>
@@ -9399,10 +9399,10 @@
         <v>0.2601989328202742</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.671942617312278</v>
+        <v>0.6051789621188397</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.4117436844920038</v>
+        <v>0.3449800292985655</v>
       </c>
       <c r="AH47" t="n">
         <v>0.15</v>
@@ -9474,7 +9474,7 @@
       </c>
       <c r="BD47" t="inlineStr">
         <is>
-          <t>Processo de software (+0.8083); Gestão de projetos de TIC (+0.7875); Processos de segurança da informação (+0.5236)</t>
+          <t>Processo de software (+0.8083); Gestão de projetos de TIC (+0.7875); Monitoramento e avaliação de TIC (+0.5844)</t>
         </is>
       </c>
       <c r="BE47" t="inlineStr">
@@ -13147,10 +13147,10 @@
         <v>0.05898448949927405</v>
       </c>
       <c r="H67" t="n">
-        <v>0.244316116990251</v>
+        <v>0.2226286084991179</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1853316274909769</v>
+        <v>0.1636441189998438</v>
       </c>
       <c r="J67" t="n">
         <v>0.0156579570894838</v>
@@ -13165,10 +13165,10 @@
         <v>0.1023110219090643</v>
       </c>
       <c r="N67" t="n">
-        <v>0.1144773221040048</v>
+        <v>0.07110230512173854</v>
       </c>
       <c r="O67" t="n">
-        <v>0.0121663001949405</v>
+        <v>-0.03120871678732576</v>
       </c>
       <c r="P67" t="n">
         <v>0</v>
@@ -13201,10 +13201,10 @@
         <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>0.275</v>
+        <v>0.14375</v>
       </c>
       <c r="AA67" t="n">
-        <v>0.275</v>
+        <v>0.14375</v>
       </c>
       <c r="AB67" t="n">
         <v>0.127715490388402</v>
@@ -13294,7 +13294,7 @@
       </c>
       <c r="BD67" t="inlineStr">
         <is>
-          <t>Modelo de gestão de TIC (+0.6222); Resultados de TIC (+0.4643); Planejamento de TIC (+0.2750)</t>
+          <t>Modelo de gestão de TIC (+0.6222); Resultados de TIC (+0.4643); Planejamento de TIC (+0.1437)</t>
         </is>
       </c>
       <c r="BE67" t="inlineStr">
@@ -13746,13 +13746,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" t="n">
         <v>15</v>
       </c>
       <c r="G2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -13844,13 +13844,13 @@
         <v>0.1419437973010805</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1893344118194827</v>
+        <v>0.1894786325594318</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1310647725067063</v>
+        <v>0.1317981176458552</v>
       </c>
       <c r="G2" t="n">
-        <v>0.009218471690280221</v>
+        <v>0.009362692430229344</v>
       </c>
       <c r="H2" t="n">
         <v>-0.003615056546364903</v>
@@ -13883,13 +13883,13 @@
         <v>0.1107410365535664</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1622522754991274</v>
+        <v>0.1636632830105264</v>
       </c>
       <c r="F3" t="n">
         <v>0.09799077653095961</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01104538177843104</v>
+        <v>0.01245638928983009</v>
       </c>
       <c r="H3" t="n">
         <v>-0.004320705738215636</v>
@@ -13922,22 +13922,22 @@
         <v>0.1633936074882846</v>
       </c>
       <c r="E4" t="n">
-        <v>0.216416548139838</v>
+        <v>0.2152939821083372</v>
       </c>
       <c r="F4" t="n">
         <v>0.1533631689949307</v>
       </c>
       <c r="G4" t="n">
-        <v>0.007391561602129413</v>
+        <v>0.006268995570628605</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.006359279569859079</v>
+        <v>-0.01486210988396745</v>
       </c>
       <c r="I4" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -13961,13 +13961,13 @@
         <v>0.15</v>
       </c>
       <c r="E5" t="n">
-        <v>0.20890522875817</v>
+        <v>0.2094771241830065</v>
       </c>
       <c r="F5" t="n">
         <v>0.1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03129084967320261</v>
+        <v>0.03186274509803921</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -14000,13 +14000,13 @@
         <v>0.03599311707714975</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1013942278998334</v>
+        <v>0.1049229648681814</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02361017767737231</v>
+        <v>0.02713891464572033</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -14078,13 +14078,13 @@
         <v>0.15</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3934742647058823</v>
+        <v>0.3902941176470588</v>
       </c>
       <c r="F8" t="n">
         <v>0.3</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1001006652661065</v>
+        <v>0.09692051820728291</v>
       </c>
       <c r="H8" t="n">
         <v>0.04791666666666666</v>
@@ -14156,22 +14156,22 @@
         <v>0.1056736956852704</v>
       </c>
       <c r="E10" t="n">
-        <v>0.185108855692459</v>
+        <v>0.1843031530403262</v>
       </c>
       <c r="F10" t="n">
         <v>0.1010912703084124</v>
       </c>
       <c r="G10" t="n">
-        <v>0.03552659022274707</v>
+        <v>0.03472088757061433</v>
       </c>
       <c r="H10" t="n">
-        <v>0.001033627972744717</v>
+        <v>0.005612016667236021</v>
       </c>
       <c r="I10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K10" t="n">
         <v>3</v>
@@ -14312,16 +14312,16 @@
         <v>0.1212478595974801</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2192856772710168</v>
+        <v>0.2183743800332565</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1741985329641795</v>
+        <v>0.1744394496296493</v>
       </c>
       <c r="G14" t="n">
-        <v>0.04749533144342098</v>
+        <v>0.04658403420566064</v>
       </c>
       <c r="H14" t="n">
-        <v>0.04185911289776773</v>
+        <v>0.04249618629911547</v>
       </c>
       <c r="I14" t="n">
         <v>40</v>
@@ -14429,13 +14429,13 @@
         <v>0.3820685911901328</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2496871528430354</v>
+        <v>0.2492692191360135</v>
       </c>
       <c r="F17" t="n">
         <v>0.1249239775786869</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2069208957921288</v>
+        <v>-0.2073388294991507</v>
       </c>
       <c r="H17" t="n">
         <v>-0.2278742117981037</v>
@@ -14520,10 +14520,10 @@
         <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -15483,10 +15483,10 @@
         <v>0.553945959583809</v>
       </c>
       <c r="K5" t="n">
-        <v>0.417536073251657</v>
+        <v>0.4034908296573994</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.136409886332152</v>
+        <v>-0.1504551299264096</v>
       </c>
       <c r="M5" t="n">
         <v>0.4339385533163037</v>
@@ -15501,10 +15501,10 @@
         <v>0.6739533658513143</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3660467726535935</v>
+        <v>0.3379562854650782</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.3079065931977208</v>
+        <v>-0.335997080386236</v>
       </c>
       <c r="S5" t="n">
         <v>0.5</v>
@@ -15537,10 +15537,10 @@
         <v>1</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7025</v>
+        <v>0.6174999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.2975</v>
+        <v>-0.3825000000000001</v>
       </c>
       <c r="AE5" t="n">
         <v>0.7466798465063026</v>
@@ -16428,10 +16428,10 @@
         <v>0.4092267544642821</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6636765201862554</v>
+        <v>0.6759476251518357</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2544497657219733</v>
+        <v>0.2667208706875536</v>
       </c>
       <c r="M10" t="n">
         <v>0.5410969924372614</v>
@@ -16446,10 +16446,10 @@
         <v>0.2773565164913028</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4906916957598171</v>
+        <v>0.5152339056909777</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2133351792685143</v>
+        <v>0.2378773891996749</v>
       </c>
       <c r="S10" t="n">
         <v>0.7166666666666667</v>
@@ -16482,10 +16482,10 @@
         <v>0.4130952380952381</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.915</v>
+        <v>1</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.5019047619047619</v>
+        <v>0.5869047619047618</v>
       </c>
       <c r="AE10" t="n">
         <v>0.2474883688541739</v>
@@ -16500,10 +16500,10 @@
         <v>0.1203922953183441</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.5733156286047514</v>
+        <v>0.5282490061751518</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.4529233332864073</v>
+        <v>0.4078567108568077</v>
       </c>
       <c r="AK10" t="n">
         <v>0.2916666666666666</v>
@@ -16536,10 +16536,10 @@
         <v>0.461087366589325</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.6249681045705874</v>
+        <v>0.5994298960423504</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.1638807379812623</v>
+        <v>0.1383425294530254</v>
       </c>
       <c r="AW10" t="n">
         <v>0.05</v>
@@ -17550,10 +17550,10 @@
         <v>0.6246033058004061</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.167173482808753</v>
+        <v>0.138753990731265</v>
       </c>
       <c r="BE17" t="n">
-        <v>-0.4574298229916531</v>
+        <v>-0.4858493150691411</v>
       </c>
     </row>
     <row r="18">
@@ -18171,10 +18171,10 @@
         <v>0.2459554087171204</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3018951793437764</v>
+        <v>0.3054830036092623</v>
       </c>
       <c r="L21" t="n">
-        <v>0.05593977062665603</v>
+        <v>0.05952759489214191</v>
       </c>
       <c r="M21" t="n">
         <v>0.0327821959341698</v>
@@ -18189,10 +18189,10 @@
         <v>0.4591286215000709</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.4132183981714049</v>
+        <v>0.4203940467023767</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.04591022332866607</v>
+        <v>-0.03873457479769427</v>
       </c>
       <c r="S21" t="n">
         <v>0.05</v>
@@ -18243,10 +18243,10 @@
         <v>0.1500000000000001</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.1146545354858269</v>
+        <v>0.2167636551934384</v>
       </c>
       <c r="AJ21" t="n">
-        <v>-0.03534546451417324</v>
+        <v>0.06676365519343827</v>
       </c>
       <c r="AK21" t="n">
         <v>0.15</v>
@@ -18279,10 +18279,10 @@
         <v>0.15</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.1745340408288195</v>
+        <v>0.184298316440158</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.02453404082881949</v>
+        <v>0.03429831644015802</v>
       </c>
       <c r="AW21" t="n">
         <v>0.15</v>
@@ -18626,10 +18626,10 @@
         <v>0.08707115530501731</v>
       </c>
       <c r="K24" t="n">
-        <v>0.05391629137736587</v>
+        <v>0.05396013116243505</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.03315486392765144</v>
+        <v>-0.03311102414258226</v>
       </c>
       <c r="M24" t="n">
         <v>0.1200443376860425</v>
@@ -18644,10 +18644,10 @@
         <v>0.05409797292399215</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.1078325827547317</v>
+        <v>0.1079202623248701</v>
       </c>
       <c r="R24" t="n">
-        <v>0.05373460983073956</v>
+        <v>0.05382228940087796</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -18734,10 +18734,10 @@
         <v>0.02202601891170285</v>
       </c>
       <c r="AU24" t="n">
-        <v>0.1597642756113385</v>
+        <v>0.1646464134170078</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.1377382566996356</v>
+        <v>0.1426203945053049</v>
       </c>
       <c r="AW24" t="n">
         <v>0</v>
@@ -19004,10 +19004,10 @@
         <v>0.2116562372713717</v>
       </c>
       <c r="K26" t="n">
-        <v>0.2778395755053683</v>
+        <v>0.2758361132448119</v>
       </c>
       <c r="L26" t="n">
-        <v>0.06618333823399661</v>
+        <v>0.06417987597344019</v>
       </c>
       <c r="M26" t="n">
         <v>0.1107410365535664</v>
@@ -19022,10 +19022,10 @@
         <v>0.312571437989177</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.3185729436556963</v>
+        <v>0.3145660191345835</v>
       </c>
       <c r="R26" t="n">
-        <v>0.006001505666519247</v>
+        <v>0.00199458114540646</v>
       </c>
       <c r="S26" t="n">
         <v>0.15</v>
@@ -19076,10 +19076,10 @@
         <v>0.3879760135726121</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.5244755941505904</v>
+        <v>0.4794089717209908</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.1364995805779783</v>
+        <v>0.09143295814837865</v>
       </c>
       <c r="AK26" t="n">
         <v>0.15</v>
@@ -19112,10 +19112,10 @@
         <v>0.1009335249995757</v>
       </c>
       <c r="AU26" t="n">
-        <v>0.5491780097330067</v>
+        <v>0.4981015926765328</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.448244484733431</v>
+        <v>0.3971680676769571</v>
       </c>
       <c r="AW26" t="n">
         <v>0.15</v>
@@ -22371,10 +22371,10 @@
         <v>0.6777257448181767</v>
       </c>
       <c r="K45" t="n">
-        <v>0.5530063887842832</v>
+        <v>0.5389611451900256</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.1247193560338935</v>
+        <v>-0.1387645996281511</v>
       </c>
       <c r="M45" t="n">
         <v>0.7014689449943675</v>
@@ -22389,10 +22389,10 @@
         <v>0.6539825446419859</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.4942140488102346</v>
+        <v>0.4661235616217193</v>
       </c>
       <c r="R45" t="n">
-        <v>-0.1597684958317513</v>
+        <v>-0.1878589830202666</v>
       </c>
       <c r="S45" t="n">
         <v>0.9055555555555556</v>
@@ -22425,10 +22425,10 @@
         <v>0.6053571428571428</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.8300000000000001</v>
+        <v>0.745</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.2246428571428573</v>
+        <v>0.1396428571428572</v>
       </c>
       <c r="AE45" t="n">
         <v>0.7885170495992505</v>
@@ -23316,10 +23316,10 @@
         <v>0.04263031711956485</v>
       </c>
       <c r="K50" t="n">
-        <v>0.1806676605496295</v>
+        <v>0.1947129041438871</v>
       </c>
       <c r="L50" t="n">
-        <v>0.1380373434300646</v>
+        <v>0.1520825870243222</v>
       </c>
       <c r="M50" t="n">
         <v>0.0469738712684514</v>
@@ -23334,10 +23334,10 @@
         <v>0.0382867629706783</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.309962604565201</v>
+        <v>0.3380530917537163</v>
       </c>
       <c r="R50" t="n">
-        <v>0.2716758415945227</v>
+        <v>0.299766328783038</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -23370,10 +23370,10 @@
         <v>0.075</v>
       </c>
       <c r="AC50" t="n">
-        <v>0.42625</v>
+        <v>0.51125</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.35125</v>
+        <v>0.43625</v>
       </c>
       <c r="AE50" t="n">
         <v>0.03540735591510425</v>
@@ -23505,19 +23505,19 @@
         <v>0.1933337468966435</v>
       </c>
       <c r="K51" t="n">
-        <v>0.1293393206258521</v>
+        <v>0.13599874684323</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.06399442627079135</v>
+        <v>-0.05733500005341347</v>
       </c>
       <c r="M51" t="n">
         <v>0.2465983387501051</v>
       </c>
       <c r="N51" t="n">
-        <v>0.1518389316326444</v>
+        <v>0.1651577840674002</v>
       </c>
       <c r="O51" t="n">
-        <v>-0.0947594071174607</v>
+        <v>-0.08144055468270489</v>
       </c>
       <c r="P51" t="n">
         <v>0.1400691550431818</v>
@@ -23532,10 +23532,10 @@
         <v>0.3444444444444444</v>
       </c>
       <c r="T51" t="n">
-        <v>0.2277777777777778</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="U51" t="n">
-        <v>-0.1166666666666666</v>
+        <v>-0.07777777777777772</v>
       </c>
       <c r="V51" t="n">
         <v>0.07798508700049113</v>
@@ -23876,35 +23876,35 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Iniciando</t>
+          <t>Intermediário</t>
         </is>
       </c>
       <c r="J53" t="n">
         <v>0.1873441488767208</v>
       </c>
       <c r="K53" t="n">
-        <v>0.3961517396969197</v>
+        <v>0.421132769125894</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2088075908201989</v>
+        <v>0.2337886202491732</v>
       </c>
       <c r="M53" t="n">
         <v>0.06376716528511499</v>
       </c>
       <c r="N53" t="n">
-        <v>0.2159932093886675</v>
+        <v>0.2986228677290474</v>
       </c>
       <c r="O53" t="n">
-        <v>0.1522260441035525</v>
+        <v>0.2348557024439324</v>
       </c>
       <c r="P53" t="n">
         <v>0.3109211324683265</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.576310270005172</v>
+        <v>0.5436426705227406</v>
       </c>
       <c r="R53" t="n">
-        <v>0.2653891375368455</v>
+        <v>0.2327215380544141</v>
       </c>
       <c r="S53" t="n">
         <v>0.15</v>
@@ -23919,10 +23919,10 @@
         <v>0.03599311707714975</v>
       </c>
       <c r="W53" t="n">
-        <v>0.380399470228791</v>
+        <v>0.620353584076456</v>
       </c>
       <c r="X53" t="n">
-        <v>0.3444063531516413</v>
+        <v>0.5843604669993063</v>
       </c>
       <c r="Y53" t="n">
         <v>0</v>
@@ -23937,10 +23937,10 @@
         <v>0.5142857142857142</v>
       </c>
       <c r="AC53" t="n">
-        <v>0.915</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="AD53" t="n">
-        <v>0.4007142857142858</v>
+        <v>0.3157142857142858</v>
       </c>
       <c r="AE53" t="n">
         <v>0.3276261949251849</v>
@@ -23955,10 +23955,10 @@
         <v>0.2601989328202742</v>
       </c>
       <c r="AI53" t="n">
-        <v>0.671942617312278</v>
+        <v>0.6051789621188397</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0.4117436844920038</v>
+        <v>0.3449800292985655</v>
       </c>
       <c r="AK53" t="n">
         <v>0.15</v>
@@ -27971,10 +27971,10 @@
         <v>0.05898448949927405</v>
       </c>
       <c r="K77" t="n">
-        <v>0.244316116990251</v>
+        <v>0.2226286084991179</v>
       </c>
       <c r="L77" t="n">
-        <v>0.1853316274909769</v>
+        <v>0.1636441189998438</v>
       </c>
       <c r="M77" t="n">
         <v>0.0156579570894838</v>
@@ -27989,10 +27989,10 @@
         <v>0.1023110219090643</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.1144773221040048</v>
+        <v>0.07110230512173854</v>
       </c>
       <c r="R77" t="n">
-        <v>0.0121663001949405</v>
+        <v>-0.03120871678732576</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -28025,10 +28025,10 @@
         <v>0</v>
       </c>
       <c r="AC77" t="n">
-        <v>0.275</v>
+        <v>0.14375</v>
       </c>
       <c r="AD77" t="n">
-        <v>0.275</v>
+        <v>0.14375</v>
       </c>
       <c r="AE77" t="n">
         <v>0.127715490388402</v>
